--- a/assets/templates/SDD_master_template.xlsx
+++ b/assets/templates/SDD_master_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\901810\GitHub\timesheet-generator\assets\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E84C268-BC53-495F-99FD-F6E480452449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60E22CF-A027-4724-A652-633BAE558338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -542,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -601,15 +601,140 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -618,247 +743,86 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="21" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="17" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="17" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="17" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="12" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1169,8 +1133,8 @@
       <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" ht="14.4">
-      <c r="A2" s="29"/>
-      <c r="B2" s="24"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
         <v>1</v>
@@ -1202,8 +1166,8 @@
       <c r="AA2" s="1"/>
     </row>
     <row r="3" spans="1:27" ht="14.4">
-      <c r="A3" s="29"/>
-      <c r="B3" s="24"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="64"/>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
         <v>2</v>
@@ -1334,8 +1298,8 @@
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="1:27" ht="14.4">
-      <c r="A7" s="29"/>
-      <c r="B7" s="24"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -1435,43 +1399,43 @@
       <c r="AA9" s="1"/>
     </row>
     <row r="10" spans="1:27" ht="14.4">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="70" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="33" t="s">
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="33" t="s">
+      <c r="L10" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="32" t="s">
+      <c r="M10" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="28" t="s">
+      <c r="N10" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="34"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="74"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -1484,11 +1448,11 @@
       <c r="AA10" s="1"/>
     </row>
     <row r="11" spans="1:27" ht="14.4">
-      <c r="A11" s="31"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
       <c r="F11" s="9" t="s">
         <v>22</v>
       </c>
@@ -1504,13 +1468,13 @@
       <c r="J11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="34"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="75"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="74"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -1523,34 +1487,34 @@
       <c r="AA11" s="1"/>
     </row>
     <row r="12" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A12" s="36">
+      <c r="A12" s="20">
         <v>1</v>
       </c>
-      <c r="B12" s="37">
-        <v>46174</v>
+      <c r="B12" s="21">
+        <v>46204</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="23">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="23">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="23">
         <f>D12-C12</f>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="45"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="77"/>
+      <c r="P12" s="77"/>
+      <c r="Q12" s="77"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -1563,34 +1527,34 @@
       <c r="AA12" s="1"/>
     </row>
     <row r="13" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A13" s="36">
+      <c r="A13" s="20">
         <v>2</v>
       </c>
-      <c r="B13" s="37">
-        <v>46175</v>
+      <c r="B13" s="21">
+        <v>46205</v>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="23">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="23">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="23">
         <f>D13-C13</f>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="87"/>
+      <c r="O13" s="87"/>
+      <c r="P13" s="87"/>
+      <c r="Q13" s="87"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -1603,34 +1567,34 @@
       <c r="AA13" s="1"/>
     </row>
     <row r="14" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A14" s="36">
+      <c r="A14" s="20">
         <v>3</v>
       </c>
-      <c r="B14" s="37">
-        <v>46176</v>
+      <c r="B14" s="21">
+        <v>46206</v>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="23">
         <v>0.33333333333333331</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="22">
         <v>0.70833333333333337</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="23">
         <f t="shared" ref="E14:E42" si="0">D14-C14</f>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="88"/>
+      <c r="O14" s="88"/>
+      <c r="P14" s="88"/>
+      <c r="Q14" s="88"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -1643,34 +1607,34 @@
       <c r="AA14" s="1"/>
     </row>
     <row r="15" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A15" s="36">
+      <c r="A15" s="20">
         <v>4</v>
       </c>
-      <c r="B15" s="37">
-        <v>46177</v>
+      <c r="B15" s="21">
+        <v>46207</v>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="88"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="88"/>
+      <c r="Q15" s="88"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -1683,34 +1647,34 @@
       <c r="AA15" s="1"/>
     </row>
     <row r="16" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A16" s="36">
+      <c r="A16" s="20">
         <v>5</v>
       </c>
-      <c r="B16" s="37">
-        <v>46178</v>
+      <c r="B16" s="21">
+        <v>46208</v>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="114"/>
-      <c r="O16" s="114"/>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="114"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -1723,34 +1687,34 @@
       <c r="AA16" s="1"/>
     </row>
     <row r="17" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A17" s="36">
+      <c r="A17" s="20">
         <v>6</v>
       </c>
-      <c r="B17" s="37">
-        <v>46179</v>
+      <c r="B17" s="21">
+        <v>46209</v>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="49"/>
-      <c r="Q17" s="50"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61"/>
+      <c r="Q17" s="62"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -1763,34 +1727,34 @@
       <c r="AA17" s="1"/>
     </row>
     <row r="18" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A18" s="36">
+      <c r="A18" s="20">
         <v>7</v>
       </c>
-      <c r="B18" s="37">
-        <v>46180</v>
+      <c r="B18" s="21">
+        <v>46210</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="49"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="50"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="60"/>
+      <c r="O18" s="61"/>
+      <c r="P18" s="61"/>
+      <c r="Q18" s="62"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -1803,34 +1767,34 @@
       <c r="AA18" s="1"/>
     </row>
     <row r="19" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A19" s="36">
+      <c r="A19" s="20">
         <v>8</v>
       </c>
-      <c r="B19" s="37">
-        <v>46181</v>
+      <c r="B19" s="21">
+        <v>46211</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="52"/>
-      <c r="P19" s="52"/>
-      <c r="Q19" s="53"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="85"/>
+      <c r="Q19" s="86"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1843,34 +1807,34 @@
       <c r="AA19" s="1"/>
     </row>
     <row r="20" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A20" s="36">
+      <c r="A20" s="20">
         <v>9</v>
       </c>
-      <c r="B20" s="37">
-        <v>46182</v>
+      <c r="B20" s="21">
+        <v>46212</v>
       </c>
-      <c r="C20" s="39">
+      <c r="C20" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="53"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="85"/>
+      <c r="Q20" s="86"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -1883,34 +1847,34 @@
       <c r="AA20" s="1"/>
     </row>
     <row r="21" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A21" s="36">
+      <c r="A21" s="20">
         <v>10</v>
       </c>
-      <c r="B21" s="37">
-        <v>46183</v>
+      <c r="B21" s="21">
+        <v>46213</v>
       </c>
-      <c r="C21" s="39">
+      <c r="C21" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="52"/>
-      <c r="P21" s="52"/>
-      <c r="Q21" s="53"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="85"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="86"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -1923,34 +1887,34 @@
       <c r="AA21" s="1"/>
     </row>
     <row r="22" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A22" s="36">
+      <c r="A22" s="20">
         <v>11</v>
       </c>
-      <c r="B22" s="57">
-        <v>46184</v>
+      <c r="B22" s="21">
+        <v>46214</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F22" s="58"/>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="59"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="59"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="61"/>
-      <c r="Q22" s="62"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="78"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="80"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -1963,34 +1927,34 @@
       <c r="AA22" s="1"/>
     </row>
     <row r="23" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A23" s="36">
+      <c r="A23" s="20">
         <v>12</v>
       </c>
-      <c r="B23" s="57">
-        <v>46185</v>
+      <c r="B23" s="21">
+        <v>46215</v>
       </c>
-      <c r="C23" s="39">
+      <c r="C23" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="59"/>
-      <c r="J23" s="59"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="59"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="61"/>
-      <c r="P23" s="61"/>
-      <c r="Q23" s="62"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="78"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="80"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -2003,34 +1967,34 @@
       <c r="AA23" s="1"/>
     </row>
     <row r="24" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A24" s="63">
+      <c r="A24" s="31">
         <v>13</v>
       </c>
-      <c r="B24" s="64">
-        <v>46186</v>
+      <c r="B24" s="21">
+        <v>46216</v>
       </c>
-      <c r="C24" s="39">
+      <c r="C24" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D24" s="38">
+      <c r="D24" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="65"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="65"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="50"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="60"/>
+      <c r="O24" s="61"/>
+      <c r="P24" s="61"/>
+      <c r="Q24" s="62"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -2043,34 +2007,34 @@
       <c r="AA24" s="1"/>
     </row>
     <row r="25" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A25" s="66">
+      <c r="A25" s="33">
         <v>14</v>
       </c>
-      <c r="B25" s="67">
-        <v>46187</v>
+      <c r="B25" s="21">
+        <v>46217</v>
       </c>
-      <c r="C25" s="39">
+      <c r="C25" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="49"/>
-      <c r="Q25" s="50"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="60"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="61"/>
+      <c r="Q25" s="62"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
@@ -2083,34 +2047,34 @@
       <c r="AA25" s="1"/>
     </row>
     <row r="26" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A26" s="36">
+      <c r="A26" s="20">
         <v>15</v>
       </c>
-      <c r="B26" s="37">
-        <v>46188</v>
+      <c r="B26" s="21">
+        <v>46218</v>
       </c>
-      <c r="C26" s="39">
+      <c r="C26" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E26" s="39">
+      <c r="E26" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="70"/>
-      <c r="P26" s="70"/>
-      <c r="Q26" s="71"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="92"/>
+      <c r="O26" s="93"/>
+      <c r="P26" s="93"/>
+      <c r="Q26" s="94"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
@@ -2123,34 +2087,34 @@
       <c r="AA26" s="1"/>
     </row>
     <row r="27" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A27" s="36">
+      <c r="A27" s="20">
         <v>16</v>
       </c>
-      <c r="B27" s="37">
-        <v>46189</v>
+      <c r="B27" s="21">
+        <v>46219</v>
       </c>
-      <c r="C27" s="39">
+      <c r="C27" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E27" s="39">
+      <c r="E27" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="73"/>
-      <c r="P27" s="73"/>
-      <c r="Q27" s="74"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="60"/>
+      <c r="O27" s="95"/>
+      <c r="P27" s="95"/>
+      <c r="Q27" s="96"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -2163,34 +2127,34 @@
       <c r="AA27" s="1"/>
     </row>
     <row r="28" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A28" s="36">
+      <c r="A28" s="20">
         <v>17</v>
       </c>
-      <c r="B28" s="75">
-        <v>46190</v>
+      <c r="B28" s="21">
+        <v>46220</v>
       </c>
-      <c r="C28" s="39">
+      <c r="C28" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="52"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="53"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="85"/>
+      <c r="Q28" s="86"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -2203,34 +2167,34 @@
       <c r="AA28" s="1"/>
     </row>
     <row r="29" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A29" s="77">
+      <c r="A29" s="14">
         <v>18</v>
       </c>
-      <c r="B29" s="78">
-        <v>46191</v>
+      <c r="B29" s="21">
+        <v>46221</v>
       </c>
-      <c r="C29" s="39">
+      <c r="C29" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E29" s="39">
+      <c r="E29" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F29" s="79"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="53"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="85"/>
+      <c r="Q29" s="86"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -2243,34 +2207,34 @@
       <c r="AA29" s="1"/>
     </row>
     <row r="30" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A30" s="66">
+      <c r="A30" s="33">
         <v>19</v>
       </c>
-      <c r="B30" s="67">
-        <v>46192</v>
+      <c r="B30" s="21">
+        <v>46222</v>
       </c>
-      <c r="C30" s="39">
+      <c r="C30" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="53"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="85"/>
+      <c r="P30" s="85"/>
+      <c r="Q30" s="86"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -2283,34 +2247,34 @@
       <c r="AA30" s="1"/>
     </row>
     <row r="31" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A31" s="36">
+      <c r="A31" s="20">
         <v>20</v>
       </c>
-      <c r="B31" s="37">
-        <v>46193</v>
+      <c r="B31" s="21">
+        <v>46223</v>
       </c>
-      <c r="C31" s="39">
+      <c r="C31" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="81"/>
-      <c r="Q31" s="82"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="82"/>
+      <c r="P31" s="82"/>
+      <c r="Q31" s="83"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -2323,34 +2287,34 @@
       <c r="AA31" s="1"/>
     </row>
     <row r="32" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A32" s="36">
+      <c r="A32" s="20">
         <v>21</v>
       </c>
-      <c r="B32" s="37">
-        <v>46194</v>
+      <c r="B32" s="21">
+        <v>46224</v>
       </c>
-      <c r="C32" s="39">
+      <c r="C32" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E32" s="39">
+      <c r="E32" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="80"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="81"/>
-      <c r="Q32" s="82"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="82"/>
+      <c r="P32" s="82"/>
+      <c r="Q32" s="83"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -2363,34 +2327,34 @@
       <c r="AA32" s="1"/>
     </row>
     <row r="33" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A33" s="36">
+      <c r="A33" s="20">
         <v>22</v>
       </c>
-      <c r="B33" s="37">
-        <v>46195</v>
+      <c r="B33" s="21">
+        <v>46225</v>
       </c>
-      <c r="C33" s="39">
+      <c r="C33" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="44"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="84"/>
-      <c r="P33" s="84"/>
-      <c r="Q33" s="85"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="89"/>
+      <c r="O33" s="90"/>
+      <c r="P33" s="90"/>
+      <c r="Q33" s="91"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -2403,34 +2367,34 @@
       <c r="AA33" s="1"/>
     </row>
     <row r="34" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A34" s="86">
+      <c r="A34" s="38">
         <v>23</v>
       </c>
-      <c r="B34" s="87">
-        <v>46196</v>
+      <c r="B34" s="21">
+        <v>46226</v>
       </c>
-      <c r="C34" s="39">
+      <c r="C34" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="88"/>
-      <c r="J34" s="88"/>
-      <c r="K34" s="89"/>
-      <c r="L34" s="90"/>
-      <c r="M34" s="91"/>
-      <c r="N34" s="92"/>
-      <c r="O34" s="93"/>
-      <c r="P34" s="93"/>
-      <c r="Q34" s="93"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="59"/>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -2443,34 +2407,34 @@
       <c r="AA34" s="1"/>
     </row>
     <row r="35" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A35" s="94">
+      <c r="A35" s="43">
         <v>24</v>
       </c>
-      <c r="B35" s="95">
-        <v>46197</v>
+      <c r="B35" s="21">
+        <v>46227</v>
       </c>
-      <c r="C35" s="39">
+      <c r="C35" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E35" s="39">
+      <c r="E35" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F35" s="96"/>
-      <c r="G35" s="96"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
-      <c r="J35" s="96"/>
-      <c r="K35" s="89"/>
-      <c r="L35" s="90"/>
-      <c r="M35" s="97"/>
-      <c r="N35" s="92"/>
-      <c r="O35" s="93"/>
-      <c r="P35" s="93"/>
-      <c r="Q35" s="93"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
+      <c r="I35" s="44"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="40"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="45"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="59"/>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="59"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -2483,34 +2447,34 @@
       <c r="AA35" s="1"/>
     </row>
     <row r="36" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A36" s="66">
+      <c r="A36" s="33">
         <v>25</v>
       </c>
-      <c r="B36" s="67">
-        <v>46198</v>
+      <c r="B36" s="21">
+        <v>46228</v>
       </c>
-      <c r="C36" s="39">
+      <c r="C36" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D36" s="38">
+      <c r="D36" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E36" s="39">
+      <c r="E36" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F36" s="98"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="99"/>
-      <c r="J36" s="99"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="44"/>
-      <c r="M36" s="100"/>
-      <c r="N36" s="92"/>
-      <c r="O36" s="93"/>
-      <c r="P36" s="93"/>
-      <c r="Q36" s="93"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="47"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="59"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="59"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
@@ -2523,34 +2487,34 @@
       <c r="AA36" s="1"/>
     </row>
     <row r="37" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A37" s="66">
+      <c r="A37" s="33">
         <v>26</v>
       </c>
-      <c r="B37" s="67">
-        <v>46199</v>
+      <c r="B37" s="21">
+        <v>46229</v>
       </c>
-      <c r="C37" s="39">
+      <c r="C37" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E37" s="39">
+      <c r="E37" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F37" s="98"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="99"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="44"/>
-      <c r="M37" s="100"/>
-      <c r="N37" s="92"/>
-      <c r="O37" s="93"/>
-      <c r="P37" s="93"/>
-      <c r="Q37" s="93"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="47"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="59"/>
+      <c r="P37" s="59"/>
+      <c r="Q37" s="59"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
@@ -2563,34 +2527,34 @@
       <c r="AA37" s="1"/>
     </row>
     <row r="38" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A38" s="66">
+      <c r="A38" s="33">
         <v>27</v>
       </c>
-      <c r="B38" s="67">
-        <v>46200</v>
+      <c r="B38" s="21">
+        <v>46230</v>
       </c>
-      <c r="C38" s="39">
+      <c r="C38" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E38" s="39">
+      <c r="E38" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F38" s="98"/>
-      <c r="G38" s="99"/>
-      <c r="H38" s="99"/>
-      <c r="I38" s="99"/>
-      <c r="J38" s="99"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="44"/>
-      <c r="M38" s="100"/>
-      <c r="N38" s="80"/>
-      <c r="O38" s="81"/>
-      <c r="P38" s="81"/>
-      <c r="Q38" s="82"/>
+      <c r="F38" s="46"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="47"/>
+      <c r="I38" s="47"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="81"/>
+      <c r="O38" s="82"/>
+      <c r="P38" s="82"/>
+      <c r="Q38" s="83"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
@@ -2603,34 +2567,34 @@
       <c r="AA38" s="1"/>
     </row>
     <row r="39" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A39" s="66">
+      <c r="A39" s="33">
         <v>28</v>
       </c>
-      <c r="B39" s="67">
-        <v>46201</v>
+      <c r="B39" s="21">
+        <v>46231</v>
       </c>
-      <c r="C39" s="39">
+      <c r="C39" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E39" s="39">
+      <c r="E39" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F39" s="98"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="99"/>
-      <c r="I39" s="99"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="100"/>
-      <c r="N39" s="80"/>
-      <c r="O39" s="81"/>
-      <c r="P39" s="81"/>
-      <c r="Q39" s="82"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="47"/>
+      <c r="I39" s="47"/>
+      <c r="J39" s="47"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="48"/>
+      <c r="N39" s="81"/>
+      <c r="O39" s="82"/>
+      <c r="P39" s="82"/>
+      <c r="Q39" s="83"/>
       <c r="R39" s="1"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
@@ -2643,34 +2607,34 @@
       <c r="AA39" s="1"/>
     </row>
     <row r="40" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A40" s="66">
+      <c r="A40" s="33">
         <v>29</v>
       </c>
-      <c r="B40" s="67">
-        <v>46202</v>
+      <c r="B40" s="21">
+        <v>46232</v>
       </c>
-      <c r="C40" s="39">
+      <c r="C40" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D40" s="38">
+      <c r="D40" s="22">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E40" s="39">
+      <c r="E40" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F40" s="98"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="100"/>
-      <c r="N40" s="101"/>
-      <c r="O40" s="102"/>
-      <c r="P40" s="102"/>
-      <c r="Q40" s="103"/>
+      <c r="F40" s="46"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="47"/>
+      <c r="I40" s="47"/>
+      <c r="J40" s="47"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="100"/>
+      <c r="O40" s="101"/>
+      <c r="P40" s="101"/>
+      <c r="Q40" s="102"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
@@ -2683,34 +2647,34 @@
       <c r="AA40" s="1"/>
     </row>
     <row r="41" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A41" s="104">
+      <c r="A41" s="49">
         <v>30</v>
       </c>
-      <c r="B41" s="78">
-        <v>46203</v>
+      <c r="B41" s="21">
+        <v>46233</v>
       </c>
-      <c r="C41" s="39">
+      <c r="C41" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D41" s="39">
+      <c r="D41" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E41" s="39">
+      <c r="E41" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F41" s="105"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="106"/>
-      <c r="I41" s="106"/>
-      <c r="J41" s="106"/>
-      <c r="K41" s="107"/>
-      <c r="L41" s="108"/>
-      <c r="M41" s="109"/>
-      <c r="N41" s="92"/>
-      <c r="O41" s="93"/>
-      <c r="P41" s="93"/>
-      <c r="Q41" s="93"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="53"/>
+      <c r="M41" s="54"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="59"/>
+      <c r="P41" s="59"/>
+      <c r="Q41" s="59"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
@@ -2723,34 +2687,34 @@
       <c r="AA41" s="1"/>
     </row>
     <row r="42" spans="1:27" ht="64.2" customHeight="1">
-      <c r="A42" s="66">
+      <c r="A42" s="33">
         <v>31</v>
       </c>
-      <c r="B42" s="67">
-        <v>46204</v>
+      <c r="B42" s="21">
+        <v>46234</v>
       </c>
-      <c r="C42" s="39">
+      <c r="C42" s="23">
         <v>0.33333333333333298</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="23">
         <v>0.70833333333333304</v>
       </c>
-      <c r="E42" s="39">
+      <c r="E42" s="23">
         <f t="shared" si="0"/>
         <v>0.37500000000000006</v>
       </c>
-      <c r="F42" s="98"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="99"/>
-      <c r="J42" s="99"/>
-      <c r="K42" s="110"/>
-      <c r="L42" s="111"/>
-      <c r="M42" s="100"/>
-      <c r="N42" s="92"/>
-      <c r="O42" s="93"/>
-      <c r="P42" s="93"/>
-      <c r="Q42" s="93"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="47"/>
+      <c r="I42" s="47"/>
+      <c r="J42" s="47"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="48"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="59"/>
+      <c r="P42" s="59"/>
+      <c r="Q42" s="59"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
@@ -2771,15 +2735,15 @@
         <v>27</v>
       </c>
       <c r="F43" s="11">
-        <f>COUNTIF(F12:F41,"H")</f>
+        <f>COUNTIF(F12:F42,"H")</f>
         <v>0</v>
       </c>
       <c r="G43" s="11">
-        <f>COUNTIF(H12:H35,"C")</f>
+        <f>COUNTIF(G12:G42,"C")</f>
         <v>0</v>
       </c>
       <c r="H43" s="11">
-        <f>COUNTIF(H12:H35,"I")</f>
+        <f>COUNTIF(H12:H42,"I")</f>
         <v>0</v>
       </c>
       <c r="I43" s="17">
@@ -2787,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="19">
-        <f>COUNTIF(J12:J41,"L")</f>
+        <f>COUNTIF(J12:J42,"L")</f>
         <v>0</v>
       </c>
       <c r="K43" s="1"/>
@@ -2869,26 +2833,26 @@
     <row r="46" spans="1:27" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="12"/>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="25" t="s">
+      <c r="D46" s="71"/>
+      <c r="E46" s="71"/>
+      <c r="F46" s="71"/>
+      <c r="G46" s="72"/>
+      <c r="H46" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="25" t="s">
+      <c r="I46" s="71"/>
+      <c r="J46" s="71"/>
+      <c r="K46" s="72"/>
+      <c r="L46" s="70" t="s">
         <v>30</v>
       </c>
-      <c r="M46" s="27"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="24"/>
+      <c r="M46" s="72"/>
+      <c r="N46" s="73"/>
+      <c r="O46" s="64"/>
+      <c r="P46" s="64"/>
       <c r="Q46" s="1"/>
       <c r="R46" s="1"/>
       <c r="S46" s="1"/>
@@ -3051,26 +3015,26 @@
     <row r="52" spans="1:27" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="12"/>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="20" t="s">
+      <c r="D52" s="98"/>
+      <c r="E52" s="98"/>
+      <c r="F52" s="98"/>
+      <c r="G52" s="68"/>
+      <c r="H52" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="20" t="s">
+      <c r="I52" s="98"/>
+      <c r="J52" s="98"/>
+      <c r="K52" s="98"/>
+      <c r="L52" s="97" t="s">
         <v>34</v>
       </c>
-      <c r="M52" s="22"/>
-      <c r="N52" s="23"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
+      <c r="M52" s="68"/>
+      <c r="N52" s="99"/>
+      <c r="O52" s="64"/>
+      <c r="P52" s="64"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
@@ -30736,6 +30700,42 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H52:K52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="N52:P52"/>
+    <mergeCell ref="N34:Q34"/>
+    <mergeCell ref="N35:Q35"/>
+    <mergeCell ref="N36:Q36"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="N41:Q41"/>
+    <mergeCell ref="N37:Q37"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="N46:P46"/>
+    <mergeCell ref="N13:Q13"/>
+    <mergeCell ref="N14:Q14"/>
+    <mergeCell ref="N15:Q15"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="N33:Q33"/>
+    <mergeCell ref="N26:Q26"/>
+    <mergeCell ref="N27:Q27"/>
+    <mergeCell ref="N28:Q28"/>
+    <mergeCell ref="N29:Q29"/>
+    <mergeCell ref="N30:Q30"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="N17:Q17"/>
+    <mergeCell ref="N18:Q18"/>
+    <mergeCell ref="N19:Q19"/>
+    <mergeCell ref="N20:Q20"/>
+    <mergeCell ref="N22:Q22"/>
+    <mergeCell ref="N23:Q23"/>
+    <mergeCell ref="N31:Q31"/>
+    <mergeCell ref="N32:Q32"/>
+    <mergeCell ref="N24:Q24"/>
     <mergeCell ref="N42:Q42"/>
     <mergeCell ref="N25:Q25"/>
     <mergeCell ref="A2:B2"/>
@@ -30752,42 +30752,6 @@
     <mergeCell ref="M10:M11"/>
     <mergeCell ref="N10:Q11"/>
     <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="N22:Q22"/>
-    <mergeCell ref="N23:Q23"/>
-    <mergeCell ref="N31:Q31"/>
-    <mergeCell ref="N32:Q32"/>
-    <mergeCell ref="N24:Q24"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="N19:Q19"/>
-    <mergeCell ref="N20:Q20"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="N33:Q33"/>
-    <mergeCell ref="N26:Q26"/>
-    <mergeCell ref="N27:Q27"/>
-    <mergeCell ref="N28:Q28"/>
-    <mergeCell ref="N29:Q29"/>
-    <mergeCell ref="N30:Q30"/>
-    <mergeCell ref="C52:G52"/>
-    <mergeCell ref="H52:K52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="N52:P52"/>
-    <mergeCell ref="N34:Q34"/>
-    <mergeCell ref="N35:Q35"/>
-    <mergeCell ref="N36:Q36"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="N41:Q41"/>
-    <mergeCell ref="N37:Q37"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="N46:P46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="44" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
